--- a/lab_5/models/metrics/dt.xlsx
+++ b/lab_5/models/metrics/dt.xlsx
@@ -467,163 +467,163 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9217</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7088</v>
+        <v>0.737</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1854</v>
+        <v>0.2095</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3294</v>
+        <v>0.2973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2373</v>
+        <v>0.2458</v>
       </c>
       <c r="F2" t="n">
-        <v>0.202</v>
+        <v>0.2058</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2113</v>
+        <v>0.2093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.9253</v>
+        <v>0.9246</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6796</v>
+        <v>0.68</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1867</v>
+        <v>0.217</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3111</v>
+        <v>0.3286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2333</v>
+        <v>0.2614</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1966</v>
+        <v>0.2234</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2037</v>
+        <v>0.2287</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.9265</v>
+        <v>0.924</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6873</v>
+        <v>0.617</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1733</v>
+        <v>0.2095</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3133</v>
+        <v>0.3143</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2232</v>
+        <v>0.2514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1879</v>
+        <v>0.2131</v>
       </c>
       <c r="G4" t="n">
-        <v>0.197</v>
+        <v>0.2179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.9277</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7274</v>
+        <v>0.6474</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2267</v>
+        <v>0.1714</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3542</v>
+        <v>0.2609</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2764</v>
+        <v>0.2069</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2403</v>
+        <v>0.1666</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2469</v>
+        <v>0.1707</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.9314</v>
+        <v>0.9222</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6954</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1457</v>
+        <v>0.2476</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3548</v>
+        <v>0.321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2066</v>
+        <v>0.2796</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1772</v>
+        <v>0.2392</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1966</v>
+        <v>0.2414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.9275</v>
+        <v>0.9225</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6952</v>
+        <v>0.6754</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1836</v>
+        <v>0.211</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3326</v>
+        <v>0.3044</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2354</v>
+        <v>0.249</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2008</v>
+        <v>0.2096</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2111</v>
+        <v>0.2136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0021</v>
+        <v>0.0017</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0201</v>
+        <v>0.041</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0261</v>
+        <v>0.0243</v>
       </c>
       <c r="D8" t="n">
-        <v>0.019</v>
+        <v>0.0241</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0231</v>
+        <v>0.024</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0215</v>
+        <v>0.0242</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0187</v>
+        <v>0.024</v>
       </c>
     </row>
   </sheetData>
